--- a/originales/respuestas/2025/01. Calificadas/root/Terminal De Transportes.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/root/Terminal De Transportes.xlsx
@@ -418,7 +418,7 @@
     <t>¿Su entidad ha puesto a disposición de todos formación orientada al fortalecimiento de capacidades en innovación?</t>
   </si>
   <si>
-    <t>Pregunta 30</t>
+    <t>Pregunta 30.</t>
   </si>
   <si>
     <t>¿Qué estrategias o iniciativas ha implementado su entidad para fomentar una cultura de innovación entre sus funcionarios y contratistas?</t>
@@ -427,7 +427,7 @@
     <t>Procesos de formación o capacitaciones en metodologías de innovación., Espacios de ideación y cocreación con los equipos internos.</t>
   </si>
   <si>
-    <t>Pregunta 31</t>
+    <t>Pregunta 31.</t>
   </si>
   <si>
     <t>¿De qué manera ha incentivado su entidad la participación de los funcionarios y contratistas en procesos de innovación?</t>
@@ -525,7 +525,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -548,6 +548,15 @@
       <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <u/>
@@ -636,7 +645,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="28">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -676,11 +685,11 @@
     <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -697,13 +706,26 @@
     <xf borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="1" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2166,11 +2188,17 @@
         <v>109486.0</v>
       </c>
       <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
+      <c r="K4" s="11">
+        <v>3.0</v>
+      </c>
       <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
+      <c r="M4" s="11">
+        <v>3.0</v>
+      </c>
       <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
+      <c r="O4" s="11">
+        <v>3.0</v>
+      </c>
       <c r="P4" s="9"/>
       <c r="Q4" s="9"/>
       <c r="R4" s="9"/>
@@ -2217,11 +2245,17 @@
         <v>130757.0</v>
       </c>
       <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
+      <c r="K5" s="11">
+        <v>3.0</v>
+      </c>
       <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
+      <c r="M5" s="11">
+        <v>3.0</v>
+      </c>
       <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
+      <c r="O5" s="11">
+        <v>3.0</v>
+      </c>
       <c r="P5" s="9"/>
       <c r="Q5" s="9"/>
       <c r="R5" s="9"/>
@@ -2315,11 +2349,17 @@
         <v>109486.0</v>
       </c>
       <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
+      <c r="K7" s="13">
+        <v>3.0</v>
+      </c>
       <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
+      <c r="M7" s="13">
+        <v>3.0</v>
+      </c>
       <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
+      <c r="O7" s="13">
+        <v>3.0</v>
+      </c>
       <c r="P7" s="6"/>
       <c r="Q7" s="6"/>
       <c r="R7" s="6"/>
@@ -2417,11 +2457,17 @@
         <v>130757.0</v>
       </c>
       <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
+      <c r="K9" s="13">
+        <v>3.0</v>
+      </c>
       <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
+      <c r="M9" s="13">
+        <v>3.0</v>
+      </c>
       <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
+      <c r="O9" s="13">
+        <v>3.0</v>
+      </c>
       <c r="P9" s="6"/>
       <c r="Q9" s="6"/>
       <c r="R9" s="6"/>
@@ -2509,7 +2555,7 @@
       <c r="H11" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I11" s="13" t="s">
+      <c r="I11" s="14" t="s">
         <v>37</v>
       </c>
       <c r="J11" s="6"/>
@@ -2564,11 +2610,17 @@
         <v>109486.0</v>
       </c>
       <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
+      <c r="K12" s="11">
+        <v>3.0</v>
+      </c>
       <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
+      <c r="M12" s="11">
+        <v>3.0</v>
+      </c>
       <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
+      <c r="O12" s="11">
+        <v>3.0</v>
+      </c>
       <c r="P12" s="9"/>
       <c r="Q12" s="9"/>
       <c r="R12" s="9"/>
@@ -2615,11 +2667,17 @@
         <v>130757.0</v>
       </c>
       <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
+      <c r="K13" s="11">
+        <v>3.0</v>
+      </c>
       <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
+      <c r="M13" s="11">
+        <v>3.0</v>
+      </c>
       <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
+      <c r="O13" s="11">
+        <v>3.0</v>
+      </c>
       <c r="P13" s="9"/>
       <c r="Q13" s="9"/>
       <c r="R13" s="9"/>
@@ -2711,11 +2769,17 @@
         <v>109486.0</v>
       </c>
       <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
+      <c r="K15" s="13">
+        <v>3.0</v>
+      </c>
       <c r="L15" s="6"/>
-      <c r="M15" s="6"/>
+      <c r="M15" s="13">
+        <v>3.0</v>
+      </c>
       <c r="N15" s="6"/>
-      <c r="O15" s="6"/>
+      <c r="O15" s="13">
+        <v>3.0</v>
+      </c>
       <c r="P15" s="6"/>
       <c r="Q15" s="6"/>
       <c r="R15" s="6"/>
@@ -2864,11 +2928,17 @@
         <v>130757.0</v>
       </c>
       <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
+      <c r="K18" s="11">
+        <v>3.0</v>
+      </c>
       <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
+      <c r="M18" s="11">
+        <v>3.0</v>
+      </c>
       <c r="N18" s="9"/>
-      <c r="O18" s="9"/>
+      <c r="O18" s="11">
+        <v>3.0</v>
+      </c>
       <c r="P18" s="9"/>
       <c r="Q18" s="9"/>
       <c r="R18" s="9"/>
@@ -2915,11 +2985,17 @@
         <v>200.0</v>
       </c>
       <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
+      <c r="K19" s="11">
+        <v>3.0</v>
+      </c>
       <c r="L19" s="9"/>
-      <c r="M19" s="9"/>
+      <c r="M19" s="11">
+        <v>3.0</v>
+      </c>
       <c r="N19" s="9"/>
-      <c r="O19" s="9"/>
+      <c r="O19" s="11">
+        <v>3.0</v>
+      </c>
       <c r="P19" s="9"/>
       <c r="Q19" s="9"/>
       <c r="R19" s="9"/>
@@ -2966,11 +3042,17 @@
         <v>200.0</v>
       </c>
       <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
+      <c r="K20" s="11">
+        <v>3.0</v>
+      </c>
       <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
+      <c r="M20" s="11">
+        <v>3.0</v>
+      </c>
       <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
+      <c r="O20" s="11">
+        <v>3.0</v>
+      </c>
       <c r="P20" s="9"/>
       <c r="Q20" s="9"/>
       <c r="R20" s="9"/>
@@ -3017,11 +3099,17 @@
         <v>200.0</v>
       </c>
       <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
+      <c r="K21" s="11">
+        <v>3.0</v>
+      </c>
       <c r="L21" s="9"/>
-      <c r="M21" s="9"/>
+      <c r="M21" s="11">
+        <v>3.0</v>
+      </c>
       <c r="N21" s="9"/>
-      <c r="O21" s="9"/>
+      <c r="O21" s="11">
+        <v>3.0</v>
+      </c>
       <c r="P21" s="9"/>
       <c r="Q21" s="9"/>
       <c r="R21" s="9"/>
@@ -3068,11 +3156,17 @@
         <v>200.0</v>
       </c>
       <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
+      <c r="K22" s="11">
+        <v>3.0</v>
+      </c>
       <c r="L22" s="9"/>
-      <c r="M22" s="9"/>
+      <c r="M22" s="11">
+        <v>3.0</v>
+      </c>
       <c r="N22" s="9"/>
-      <c r="O22" s="9"/>
+      <c r="O22" s="11">
+        <v>3.0</v>
+      </c>
       <c r="P22" s="9"/>
       <c r="Q22" s="9"/>
       <c r="R22" s="9"/>
@@ -3170,11 +3264,17 @@
         <v>84.0</v>
       </c>
       <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
+      <c r="K24" s="13">
+        <v>3.0</v>
+      </c>
       <c r="L24" s="6"/>
-      <c r="M24" s="6"/>
+      <c r="M24" s="13">
+        <v>3.0</v>
+      </c>
       <c r="N24" s="6"/>
-      <c r="O24" s="6"/>
+      <c r="O24" s="13">
+        <v>3.0</v>
+      </c>
       <c r="P24" s="6"/>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -3221,11 +3321,17 @@
         <v>158.0</v>
       </c>
       <c r="J25" s="9"/>
-      <c r="K25" s="9"/>
+      <c r="K25" s="11">
+        <v>3.0</v>
+      </c>
       <c r="L25" s="9"/>
-      <c r="M25" s="9"/>
+      <c r="M25" s="11">
+        <v>3.0</v>
+      </c>
       <c r="N25" s="9"/>
-      <c r="O25" s="9"/>
+      <c r="O25" s="11">
+        <v>3.0</v>
+      </c>
       <c r="P25" s="9"/>
       <c r="Q25" s="9"/>
       <c r="R25" s="9"/>
@@ -3272,11 +3378,17 @@
         <v>3.0</v>
       </c>
       <c r="J26" s="6"/>
-      <c r="K26" s="6"/>
+      <c r="K26" s="13">
+        <v>3.0</v>
+      </c>
       <c r="L26" s="6"/>
-      <c r="M26" s="6"/>
+      <c r="M26" s="13">
+        <v>3.0</v>
+      </c>
       <c r="N26" s="6"/>
-      <c r="O26" s="6"/>
+      <c r="O26" s="13">
+        <v>3.0</v>
+      </c>
       <c r="P26" s="6"/>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -3323,11 +3435,17 @@
         <v>5.0</v>
       </c>
       <c r="J27" s="6"/>
-      <c r="K27" s="6"/>
+      <c r="K27" s="13">
+        <v>3.0</v>
+      </c>
       <c r="L27" s="6"/>
-      <c r="M27" s="6"/>
+      <c r="M27" s="13">
+        <v>3.0</v>
+      </c>
       <c r="N27" s="6"/>
-      <c r="O27" s="6"/>
+      <c r="O27" s="13">
+        <v>3.0</v>
+      </c>
       <c r="P27" s="6"/>
       <c r="Q27" s="6"/>
       <c r="R27" s="6"/>
@@ -3425,19 +3543,19 @@
         <v>28</v>
       </c>
       <c r="J29" s="6"/>
-      <c r="K29" s="14">
+      <c r="K29" s="13">
         <v>4.0</v>
       </c>
       <c r="L29" s="6"/>
-      <c r="M29" s="14">
+      <c r="M29" s="13">
         <v>3.0</v>
       </c>
       <c r="N29" s="6"/>
-      <c r="O29" s="14">
+      <c r="O29" s="13">
         <v>3.0</v>
       </c>
       <c r="P29" s="6"/>
-      <c r="Q29" s="14">
+      <c r="Q29" s="13">
         <v>2.0</v>
       </c>
       <c r="R29" s="6"/>
@@ -4554,7 +4672,9 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="31" width="10.71"/>
+    <col customWidth="1" min="1" max="8" width="10.71"/>
+    <col customWidth="1" min="9" max="9" width="43.43"/>
+    <col customWidth="1" min="10" max="31" width="10.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="43.5" customHeight="1">
@@ -4704,19 +4824,19 @@
         <v>28</v>
       </c>
       <c r="J3" s="6"/>
-      <c r="K3" s="14">
+      <c r="K3" s="13">
         <v>3.0</v>
       </c>
       <c r="L3" s="17"/>
-      <c r="M3" s="14">
+      <c r="M3" s="13">
         <v>3.0</v>
       </c>
       <c r="N3" s="6"/>
-      <c r="O3" s="14">
+      <c r="O3" s="13">
         <v>2.0</v>
       </c>
       <c r="P3" s="6"/>
-      <c r="Q3" s="14">
+      <c r="Q3" s="13">
         <v>3.0</v>
       </c>
       <c r="R3" s="6"/>
@@ -4896,15 +5016,25 @@
         <v>97</v>
       </c>
       <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
+      <c r="K7" s="11">
+        <v>3.0</v>
+      </c>
       <c r="L7" s="15"/>
-      <c r="M7" s="9"/>
+      <c r="M7" s="11">
+        <v>1.0</v>
+      </c>
       <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
+      <c r="O7" s="11">
+        <v>3.0</v>
+      </c>
       <c r="P7" s="9"/>
-      <c r="Q7" s="9"/>
+      <c r="Q7" s="11">
+        <v>3.0</v>
+      </c>
       <c r="R7" s="9"/>
-      <c r="S7" s="16"/>
+      <c r="S7" s="19">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="8" ht="126.75" customHeight="1">
       <c r="A8" s="6" t="s">
@@ -4935,15 +5065,25 @@
         <v>100</v>
       </c>
       <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="6"/>
-      <c r="R8" s="6"/>
-      <c r="S8" s="18"/>
+      <c r="K8" s="20">
+        <v>3.0</v>
+      </c>
+      <c r="L8" s="21"/>
+      <c r="M8" s="22">
+        <v>2.0</v>
+      </c>
+      <c r="N8" s="21"/>
+      <c r="O8" s="20">
+        <v>3.0</v>
+      </c>
+      <c r="P8" s="21"/>
+      <c r="Q8" s="20">
+        <v>3.0</v>
+      </c>
+      <c r="R8" s="21"/>
+      <c r="S8" s="23">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="9" ht="126.75" customHeight="1">
       <c r="A9" s="6" t="s">
@@ -4974,15 +5114,25 @@
         <v>103</v>
       </c>
       <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
-      <c r="Q9" s="6"/>
-      <c r="R9" s="6"/>
-      <c r="S9" s="18"/>
+      <c r="K9" s="20">
+        <v>3.0</v>
+      </c>
+      <c r="L9" s="21"/>
+      <c r="M9" s="22">
+        <v>4.0</v>
+      </c>
+      <c r="N9" s="21"/>
+      <c r="O9" s="22">
+        <v>4.0</v>
+      </c>
+      <c r="P9" s="21"/>
+      <c r="Q9" s="22">
+        <v>4.0</v>
+      </c>
+      <c r="R9" s="21"/>
+      <c r="S9" s="23">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="10" ht="126.75" customHeight="1">
       <c r="A10" s="9" t="s">
@@ -5013,15 +5163,25 @@
         <v>106</v>
       </c>
       <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
+      <c r="K10" s="11">
+        <v>3.0</v>
+      </c>
       <c r="L10" s="15"/>
-      <c r="M10" s="9"/>
+      <c r="M10" s="11">
+        <v>2.0</v>
+      </c>
       <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
+      <c r="O10" s="11">
+        <v>3.0</v>
+      </c>
       <c r="P10" s="9"/>
-      <c r="Q10" s="9"/>
+      <c r="Q10" s="11">
+        <v>4.0</v>
+      </c>
       <c r="R10" s="9"/>
-      <c r="S10" s="16"/>
+      <c r="S10" s="19">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="11" ht="126.75" customHeight="1">
       <c r="A11" s="6" t="s">
@@ -5052,15 +5212,25 @@
         <v>109</v>
       </c>
       <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
+      <c r="K11" s="13">
+        <v>3.0</v>
+      </c>
       <c r="L11" s="17"/>
-      <c r="M11" s="6"/>
+      <c r="M11" s="13">
+        <v>4.0</v>
+      </c>
       <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
+      <c r="O11" s="13">
+        <v>4.0</v>
+      </c>
       <c r="P11" s="6"/>
-      <c r="Q11" s="6"/>
+      <c r="Q11" s="13">
+        <v>3.0</v>
+      </c>
       <c r="R11" s="6"/>
-      <c r="S11" s="18"/>
+      <c r="S11" s="24">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="12" ht="126.75" customHeight="1">
       <c r="A12" s="6" t="s">
@@ -5091,15 +5261,25 @@
         <v>112</v>
       </c>
       <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
+      <c r="K12" s="13">
+        <v>3.0</v>
+      </c>
       <c r="L12" s="17"/>
-      <c r="M12" s="6"/>
+      <c r="M12" s="13">
+        <v>4.0</v>
+      </c>
       <c r="N12" s="6"/>
-      <c r="O12" s="6"/>
+      <c r="O12" s="13">
+        <v>3.0</v>
+      </c>
       <c r="P12" s="6"/>
-      <c r="Q12" s="6"/>
+      <c r="Q12" s="13">
+        <v>4.0</v>
+      </c>
       <c r="R12" s="6"/>
-      <c r="S12" s="18"/>
+      <c r="S12" s="24">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="13" ht="126.75" customHeight="1">
       <c r="A13" s="9" t="s">
@@ -5130,15 +5310,25 @@
         <v>115</v>
       </c>
       <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
+      <c r="K13" s="11">
+        <v>4.0</v>
+      </c>
       <c r="L13" s="15"/>
-      <c r="M13" s="9"/>
+      <c r="M13" s="11">
+        <v>4.0</v>
+      </c>
       <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
+      <c r="O13" s="11">
+        <v>3.0</v>
+      </c>
       <c r="P13" s="9"/>
-      <c r="Q13" s="9"/>
+      <c r="Q13" s="11">
+        <v>4.0</v>
+      </c>
       <c r="R13" s="9"/>
-      <c r="S13" s="16"/>
+      <c r="S13" s="19">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="14" ht="126.75" customHeight="1">
       <c r="A14" s="9" t="s">
@@ -5169,15 +5359,25 @@
         <v>118</v>
       </c>
       <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
+      <c r="K14" s="11">
+        <v>4.0</v>
+      </c>
       <c r="L14" s="15"/>
-      <c r="M14" s="9"/>
+      <c r="M14" s="11">
+        <v>3.0</v>
+      </c>
       <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
+      <c r="O14" s="11">
+        <v>4.0</v>
+      </c>
       <c r="P14" s="9"/>
-      <c r="Q14" s="9"/>
+      <c r="Q14" s="11">
+        <v>3.0</v>
+      </c>
       <c r="R14" s="9"/>
-      <c r="S14" s="16"/>
+      <c r="S14" s="19">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="15" ht="126.75" customHeight="1">
       <c r="A15" s="9" t="s">
@@ -5208,15 +5408,25 @@
         <v>121</v>
       </c>
       <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
+      <c r="K15" s="11">
+        <v>2.0</v>
+      </c>
       <c r="L15" s="15"/>
-      <c r="M15" s="9"/>
+      <c r="M15" s="11">
+        <v>2.0</v>
+      </c>
       <c r="N15" s="9"/>
-      <c r="O15" s="9"/>
+      <c r="O15" s="11">
+        <v>2.0</v>
+      </c>
       <c r="P15" s="9"/>
-      <c r="Q15" s="9"/>
+      <c r="Q15" s="11">
+        <v>2.0</v>
+      </c>
       <c r="R15" s="9"/>
-      <c r="S15" s="16"/>
+      <c r="S15" s="19">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="16" ht="126.75" customHeight="1">
       <c r="A16" s="9" t="s">
@@ -5320,7 +5530,7 @@
       <c r="C18" s="7">
         <v>17.0</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="13" t="s">
         <v>128</v>
       </c>
       <c r="E18" s="6"/>
@@ -5335,15 +5545,25 @@
         <v>130</v>
       </c>
       <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
+      <c r="K18" s="13">
+        <v>3.0</v>
+      </c>
       <c r="L18" s="17"/>
-      <c r="M18" s="6"/>
+      <c r="M18" s="13">
+        <v>3.0</v>
+      </c>
       <c r="N18" s="6"/>
-      <c r="O18" s="6"/>
+      <c r="O18" s="13">
+        <v>2.0</v>
+      </c>
       <c r="P18" s="6"/>
-      <c r="Q18" s="6"/>
+      <c r="Q18" s="13">
+        <v>3.0</v>
+      </c>
       <c r="R18" s="6"/>
-      <c r="S18" s="18"/>
+      <c r="S18" s="24">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="19" ht="126.75" customHeight="1">
       <c r="A19" s="9" t="s">
@@ -5353,7 +5573,7 @@
       <c r="C19" s="10">
         <v>18.0</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="11" t="s">
         <v>131</v>
       </c>
       <c r="E19" s="9"/>
@@ -5368,15 +5588,25 @@
         <v>133</v>
       </c>
       <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
+      <c r="K19" s="11">
+        <v>3.0</v>
+      </c>
       <c r="L19" s="15"/>
-      <c r="M19" s="9"/>
+      <c r="M19" s="11">
+        <v>3.0</v>
+      </c>
       <c r="N19" s="9"/>
-      <c r="O19" s="9"/>
+      <c r="O19" s="11">
+        <v>4.0</v>
+      </c>
       <c r="P19" s="9"/>
-      <c r="Q19" s="9"/>
+      <c r="Q19" s="11">
+        <v>4.0</v>
+      </c>
       <c r="R19" s="9"/>
-      <c r="S19" s="16"/>
+      <c r="S19" s="19">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="20" ht="126.75" customHeight="1">
       <c r="A20" s="9" t="s">
@@ -6558,15 +6788,25 @@
         <v>144</v>
       </c>
       <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
+      <c r="K3" s="24">
+        <v>1.0</v>
+      </c>
       <c r="L3" s="18"/>
-      <c r="M3" s="18"/>
+      <c r="M3" s="24">
+        <v>1.0</v>
+      </c>
       <c r="N3" s="18"/>
-      <c r="O3" s="18"/>
+      <c r="O3" s="24">
+        <v>1.0</v>
+      </c>
       <c r="P3" s="18"/>
-      <c r="Q3" s="18"/>
+      <c r="Q3" s="24">
+        <v>1.0</v>
+      </c>
       <c r="R3" s="18"/>
-      <c r="S3" s="18"/>
+      <c r="S3" s="24">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
     <row r="5" ht="14.25" customHeight="1"/>
@@ -7686,7 +7926,7 @@
       <c r="K2" s="19">
         <v>3.0</v>
       </c>
-      <c r="L2" s="20"/>
+      <c r="L2" s="25"/>
       <c r="M2" s="19">
         <v>3.0</v>
       </c>
@@ -7726,15 +7966,25 @@
         <v>152</v>
       </c>
       <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="21"/>
-      <c r="M3" s="18"/>
+      <c r="K3" s="24">
+        <v>3.0</v>
+      </c>
+      <c r="L3" s="26"/>
+      <c r="M3" s="24">
+        <v>3.0</v>
+      </c>
       <c r="N3" s="18"/>
-      <c r="O3" s="18"/>
+      <c r="O3" s="24">
+        <v>4.0</v>
+      </c>
       <c r="P3" s="18"/>
-      <c r="Q3" s="18"/>
+      <c r="Q3" s="24">
+        <v>4.0</v>
+      </c>
       <c r="R3" s="18"/>
-      <c r="S3" s="18"/>
+      <c r="S3" s="24">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="4" ht="126.75" customHeight="1">
       <c r="A4" s="16" t="s">
@@ -7757,12 +8007,12 @@
       <c r="H4" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="I4" s="22" t="s">
+      <c r="I4" s="27" t="s">
         <v>154</v>
       </c>
       <c r="J4" s="16"/>
       <c r="K4" s="16"/>
-      <c r="L4" s="20"/>
+      <c r="L4" s="25"/>
       <c r="M4" s="16"/>
       <c r="N4" s="16"/>
       <c r="O4" s="16"/>
@@ -7798,15 +8048,25 @@
         <v>157</v>
       </c>
       <c r="J5" s="16"/>
-      <c r="K5" s="16"/>
-      <c r="L5" s="20"/>
-      <c r="M5" s="16"/>
+      <c r="K5" s="19">
+        <v>3.0</v>
+      </c>
+      <c r="L5" s="25"/>
+      <c r="M5" s="19">
+        <v>3.0</v>
+      </c>
       <c r="N5" s="16"/>
-      <c r="O5" s="16"/>
+      <c r="O5" s="19">
+        <v>4.0</v>
+      </c>
       <c r="P5" s="16"/>
-      <c r="Q5" s="16"/>
+      <c r="Q5" s="19">
+        <v>4.0</v>
+      </c>
       <c r="R5" s="16"/>
-      <c r="S5" s="16"/>
+      <c r="S5" s="19">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="6" ht="126.75" customHeight="1">
       <c r="A6" s="16" t="s">
@@ -7829,12 +8089,12 @@
       <c r="H6" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="I6" s="22" t="s">
+      <c r="I6" s="27" t="s">
         <v>158</v>
       </c>
       <c r="J6" s="16"/>
       <c r="K6" s="16"/>
-      <c r="L6" s="20"/>
+      <c r="L6" s="25"/>
       <c r="M6" s="16"/>
       <c r="N6" s="16"/>
       <c r="O6" s="16"/>
@@ -7875,7 +8135,7 @@
       <c r="K7" s="19">
         <v>2.0</v>
       </c>
-      <c r="L7" s="20"/>
+      <c r="L7" s="25"/>
       <c r="M7" s="19">
         <v>2.0</v>
       </c>
